--- a/2025-MLS-projections/US Catch/USA_Catch.xlsx
+++ b/2025-MLS-projections/US Catch/USA_Catch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\US Catch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E727BF8E-7C66-4A81-A984-1E75B0F376AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F515D596-32FD-446B-BAB9-5F3CD11CDB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1234" yWindow="429" windowWidth="13663" windowHeight="8185" xr2:uid="{B7E737E3-9C19-4BAF-A933-783AA9D546EB}"/>
+    <workbookView xWindow="754" yWindow="754" windowWidth="13766" windowHeight="8186" xr2:uid="{B7E737E3-9C19-4BAF-A933-783AA9D546EB}"/>
   </bookViews>
   <sheets>
     <sheet name="US WCNPO MLS Catch" sheetId="6" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="155">
   <si>
     <t>report_year</t>
   </si>
@@ -429,9 +429,6 @@
     <t>est_kgs</t>
   </si>
   <si>
-    <t>US WCNPO MLS Total Catch (mt)</t>
-  </si>
-  <si>
     <t>WCNPO MLS Mean Fish Weight (kg)</t>
   </si>
   <si>
@@ -523,6 +520,15 @@
   </si>
   <si>
     <t>US Total</t>
+  </si>
+  <si>
+    <t>Total US WCNPO MLS Catch (mt)</t>
+  </si>
+  <si>
+    <t>Hawaii Longline Catch (mt)</t>
+  </si>
+  <si>
+    <t>Hawaii Non-Longline Catch (mt)</t>
   </si>
 </sst>
 </file>
@@ -577,7 +583,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,6 +599,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -780,7 +792,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -841,7 +853,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -852,7 +863,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -860,12 +870,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -998,6 +1002,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1019,18 +1035,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1391,243 +1427,232 @@
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="37.4609375" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="13" max="13" width="10.921875" customWidth="1"/>
     <col min="14" max="14" width="14.69140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
       <c r="M2" t="s">
+        <v>149</v>
+      </c>
+      <c r="N2" t="s">
         <v>150</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>151</v>
       </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="106">
+        <v>2021</v>
+      </c>
+      <c r="C3" s="24">
+        <v>2022</v>
+      </c>
+      <c r="D3" s="106">
+        <v>2023</v>
+      </c>
+      <c r="E3" s="24">
+        <v>2024</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3">
+        <v>2021</v>
+      </c>
+      <c r="L3">
+        <f t="array" ref="L3:N6">TRANSPOSE(B4:E6)</f>
+        <v>256.49358231668299</v>
+      </c>
+      <c r="M3">
+        <v>8.82</v>
+      </c>
+      <c r="N3">
+        <v>265.31358231668298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="33">
+        <v>256.49358231668299</v>
+      </c>
+      <c r="C4" s="104">
+        <v>288.540794295973</v>
+      </c>
+      <c r="D4" s="33">
+        <v>207.28263460981</v>
+      </c>
+      <c r="E4" s="104">
+        <v>565.12376371508105</v>
+      </c>
+      <c r="F4" s="33">
+        <f>AVERAGE(B4:E4)</f>
+        <v>329.36019373438671</v>
+      </c>
+      <c r="K4">
+        <v>2022</v>
+      </c>
+      <c r="L4">
+        <v>288.540794295973</v>
+      </c>
+      <c r="M4">
+        <v>9.5850000000000009</v>
+      </c>
+      <c r="N4">
+        <v>298.12579429597298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="101" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="30">
+        <v>8.82</v>
+      </c>
+      <c r="C5" s="21">
+        <v>9.5850000000000009</v>
+      </c>
+      <c r="D5" s="30">
+        <v>6.7430000000000003</v>
+      </c>
+      <c r="E5" s="21">
+        <v>18.591000000000001</v>
+      </c>
+      <c r="F5" s="30">
+        <f>AVERAGE(B5:E5)</f>
+        <v>10.934750000000001</v>
+      </c>
+      <c r="K5">
+        <v>2023</v>
+      </c>
+      <c r="L5">
+        <v>207.28263460981</v>
+      </c>
+      <c r="M5">
+        <v>6.7430000000000003</v>
+      </c>
+      <c r="N5">
+        <v>214.02563460981</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="102" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="23">
-        <v>2020</v>
-      </c>
-      <c r="C3" s="24">
-        <v>2021</v>
-      </c>
-      <c r="D3" s="24">
-        <v>2022</v>
-      </c>
-      <c r="E3" s="24">
-        <v>2023</v>
-      </c>
-      <c r="F3" s="24">
+      <c r="B6" s="97">
+        <f>B4+B5</f>
+        <v>265.31358231668298</v>
+      </c>
+      <c r="C6" s="96">
+        <f>C4+C5</f>
+        <v>298.12579429597298</v>
+      </c>
+      <c r="D6" s="97">
+        <f>D4+D5</f>
+        <v>214.02563460981</v>
+      </c>
+      <c r="E6" s="96">
+        <f>E4+E5</f>
+        <v>583.71476371508106</v>
+      </c>
+      <c r="F6" s="97">
+        <f>AVERAGE(B6:E6)</f>
+        <v>340.29494373438672</v>
+      </c>
+      <c r="K6">
         <v>2024</v>
       </c>
-      <c r="G3" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="L3">
-        <v>2021</v>
-      </c>
-      <c r="M3">
-        <f t="array" ref="M3:O6">TRANSPOSE(C4:F6)</f>
-        <v>256.49358231668299</v>
-      </c>
-      <c r="N3">
-        <v>8.82</v>
-      </c>
-      <c r="O3">
-        <v>265.31358231668298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A4" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="20">
-        <v>323.03758445389201</v>
-      </c>
-      <c r="C4" s="20">
-        <v>256.49358231668299</v>
-      </c>
-      <c r="D4" s="20">
-        <v>288.540794295973</v>
-      </c>
-      <c r="E4" s="20">
-        <v>207.28263460981</v>
-      </c>
-      <c r="F4" s="20">
+      <c r="L6">
         <v>565.12376371508105</v>
       </c>
-      <c r="G4" s="30">
-        <f>AVERAGE(B4:F4)</f>
-        <v>328.09567187828782</v>
-      </c>
-      <c r="L4">
-        <v>2022</v>
-      </c>
-      <c r="M4">
-        <v>288.540794295973</v>
-      </c>
-      <c r="N4">
-        <v>9.5850000000000009</v>
-      </c>
-      <c r="O4">
-        <v>298.12579429597298</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="21">
-        <v>9.9789999999999992</v>
-      </c>
-      <c r="C5" s="21">
-        <v>8.82</v>
-      </c>
-      <c r="D5" s="21">
-        <v>9.5850000000000009</v>
-      </c>
-      <c r="E5" s="21">
-        <v>6.7430000000000003</v>
-      </c>
-      <c r="F5" s="21">
+      <c r="M6">
         <v>18.591000000000001</v>
       </c>
-      <c r="G5" s="31">
-        <f t="shared" ref="G5:G10" si="0">AVERAGE(B5:F5)</f>
-        <v>10.743600000000001</v>
-      </c>
-      <c r="L5">
-        <v>2023</v>
-      </c>
-      <c r="M5">
-        <v>207.28263460981</v>
-      </c>
-      <c r="N5">
-        <v>6.7430000000000003</v>
-      </c>
-      <c r="O5">
-        <v>214.02563460981</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="37">
-        <f>B4+B5</f>
-        <v>333.01658445389199</v>
-      </c>
-      <c r="C6" s="37">
-        <f>C4+C5</f>
-        <v>265.31358231668298</v>
-      </c>
-      <c r="D6" s="37">
-        <f>D4+D5</f>
-        <v>298.12579429597298</v>
-      </c>
-      <c r="E6" s="37">
-        <f>E4+E5</f>
-        <v>214.02563460981</v>
-      </c>
-      <c r="F6" s="37">
-        <f>F4+F5</f>
+      <c r="N6">
         <v>583.71476371508106</v>
       </c>
-      <c r="G6" s="38">
-        <f t="shared" si="0"/>
-        <v>338.83927187828783</v>
-      </c>
-      <c r="L6">
-        <v>2024</v>
-      </c>
-      <c r="M6">
-        <v>565.12376371508105</v>
-      </c>
-      <c r="N6">
-        <v>18.591000000000001</v>
-      </c>
-      <c r="O6">
-        <v>583.71476371508106</v>
-      </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A8" s="96" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="97">
+    <row r="8" spans="1:15" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A8" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="85">
         <v>250</v>
       </c>
-      <c r="C8" s="97">
+      <c r="C8" s="85">
         <v>207</v>
       </c>
-      <c r="D8" s="97">
+      <c r="D8" s="85">
         <v>239</v>
       </c>
-      <c r="E8" s="97">
+      <c r="E8" s="85">
         <v>175</v>
       </c>
-      <c r="F8" s="97">
+      <c r="F8" s="85">
         <v>175</v>
       </c>
-      <c r="G8" s="98">
-        <f t="shared" si="0"/>
+      <c r="G8" s="86">
+        <f t="shared" ref="G8:G10" si="0">AVERAGE(B8:F8)</f>
         <v>209.2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="99">
+    <row r="9" spans="1:15" ht="58.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="99" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="87">
         <v>47</v>
       </c>
-      <c r="C9" s="99">
+      <c r="C9" s="87">
         <v>30</v>
       </c>
-      <c r="D9" s="99">
+      <c r="D9" s="87">
         <v>25</v>
       </c>
-      <c r="E9" s="99">
+      <c r="E9" s="87">
         <v>13</v>
       </c>
-      <c r="F9" s="99">
+      <c r="F9" s="87">
         <v>13</v>
       </c>
-      <c r="G9" s="100">
+      <c r="G9" s="88">
         <f t="shared" si="0"/>
         <v>25.6</v>
       </c>
       <c r="H9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="26" t="s">
-        <v>137</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="58.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="100" t="s">
+        <v>136</v>
       </c>
       <c r="B10" s="23">
         <f>SUM(B8:B9)</f>
@@ -1649,14 +1674,14 @@
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="33">
         <f t="shared" si="0"/>
         <v>234.8</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -1686,8 +1711,8 @@
       <c r="F16" s="24">
         <v>2024</v>
       </c>
-      <c r="G16" s="34" t="s">
-        <v>135</v>
+      <c r="G16" s="32" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -1709,13 +1734,13 @@
       <c r="F17" s="20">
         <v>24.196085105115646</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="29">
         <f t="shared" ref="G17:G18" si="2">AVERAGE(B17:F17)</f>
         <v>28.427837299717435</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>117</v>
       </c>
       <c r="B18" s="22">
@@ -1733,12 +1758,15 @@
       <c r="F18" s="22">
         <v>25.965083798882681</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="31">
         <f t="shared" si="2"/>
         <v>31.863863883667136</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F2"/>
+  </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -1775,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>9</v>
@@ -1784,7 +1812,7 @@
         <v>10</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>11</v>
@@ -1975,7 +2003,7 @@
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D9" s="92" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E9" s="92"/>
       <c r="F9" s="92"/>
@@ -1992,40 +2020,40 @@
       <c r="H10" s="91"/>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D11" s="39">
+      <c r="D11" s="35">
         <v>2020</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="39">
         <v>2021</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="36">
         <v>2022</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="40">
         <v>2023</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="38">
         <v>2024</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D12" s="73">
+      <c r="D12" s="69">
         <f>D7/1000</f>
         <v>323.03758445389201</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="70">
         <f>E7/1000</f>
         <v>256.49358231668299</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="71">
         <f>F7/1000</f>
         <v>288.540794295973</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="70">
         <f>G7/1000</f>
         <v>207.28263460981</v>
       </c>
-      <c r="H12" s="76">
+      <c r="H12" s="72">
         <f>H7/1000</f>
         <v>565.12376371508105</v>
       </c>
@@ -2035,7 +2063,7 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D15" s="92" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E15" s="92"/>
       <c r="F15" s="92"/>
@@ -2052,37 +2080,37 @@
       <c r="H16" s="91"/>
     </row>
     <row r="17" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D17" s="45">
+      <c r="D17" s="41">
         <v>2020</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="42">
         <v>2021</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="43">
         <v>2022</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="44">
         <v>2023</v>
       </c>
-      <c r="H17" s="49">
+      <c r="H17" s="45">
         <v>2024</v>
       </c>
     </row>
     <row r="18" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D18" s="77" cm="1">
+      <c r="D18" s="73" cm="1">
         <f t="array" ref="D18:H18">TRANSPOSE(H2:H6)</f>
         <v>29.863879490976426</v>
       </c>
-      <c r="E18" s="78">
+      <c r="E18" s="74">
         <v>28.703399990676253</v>
       </c>
-      <c r="F18" s="79">
+      <c r="F18" s="75">
         <v>27.90260074421942</v>
       </c>
-      <c r="G18" s="78">
+      <c r="G18" s="74">
         <v>31.473221167599451</v>
       </c>
-      <c r="H18" s="80">
+      <c r="H18" s="76">
         <v>24.196085105115646</v>
       </c>
     </row>
@@ -2128,25 +2156,25 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F1" t="s">
         <v>119</v>
       </c>
       <c r="G1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" t="s">
         <v>133</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>125</v>
       </c>
-      <c r="I1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>126</v>
-      </c>
-      <c r="K1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
@@ -2346,18 +2374,18 @@
     </row>
     <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="69"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="53"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="47"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="69"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="89" t="s">
         <v>58</v>
       </c>
@@ -2369,52 +2397,52 @@
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="40">
+        <v>142</v>
+      </c>
+      <c r="B10" s="36">
         <v>2020</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="36">
         <v>2021</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="36">
         <v>2022</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="37">
         <v>2023</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="38">
         <v>2024</v>
       </c>
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A11" s="63" t="s">
-        <v>140</v>
-      </c>
-      <c r="B11" s="64">
+      <c r="A11" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="60">
         <f t="array" ref="B11:F11">TRANSPOSE(E2:E6)</f>
         <v>9.9789999999999992</v>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="61">
         <v>8.82</v>
       </c>
-      <c r="D11" s="65">
+      <c r="D11" s="61">
         <v>9.5850000000000009</v>
       </c>
-      <c r="E11" s="65">
+      <c r="E11" s="61">
         <v>6.7430000000000003</v>
       </c>
-      <c r="F11" s="66">
+      <c r="F11" s="62">
         <v>18.591000000000001</v>
       </c>
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" s="54" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="61">
+      <c r="A12" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="57">
         <f t="array" ref="B12:F12">TRANSPOSE(G2:G6)</f>
         <v>6.351</v>
       </c>
@@ -2427,15 +2455,15 @@
       <c r="E12" s="21">
         <v>5.577</v>
       </c>
-      <c r="F12" s="58">
+      <c r="F12" s="54">
         <v>7.3410000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="62">
+      <c r="A13" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="58">
         <f t="array" ref="B13:F13">TRANSPOSE(I2:I6)</f>
         <v>7.8310000000000004</v>
       </c>
@@ -2448,24 +2476,24 @@
       <c r="E13" s="22">
         <v>6.8079999999999998</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="56">
         <v>8.8339999999999996</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="69"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="53"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="47"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="49"/>
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="69"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="89" t="s">
         <v>58</v>
       </c>
@@ -2476,44 +2504,44 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="68">
+      <c r="A17" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="64">
         <v>2020</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="51">
         <v>2021</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="51">
         <v>2022</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="52">
         <v>2023</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F17" s="53">
         <v>2024</v>
       </c>
       <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="B18" s="70">
+      <c r="A18" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="66">
         <f t="array" ref="B18:F18">TRANSPOSE(K2:K6)</f>
         <v>33.374581939799334</v>
       </c>
-      <c r="C18" s="71">
+      <c r="C18" s="67">
         <v>36.75</v>
       </c>
-      <c r="D18" s="71">
+      <c r="D18" s="67">
         <v>31.120129870129869</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="67">
         <v>32.109523809523807</v>
       </c>
-      <c r="F18" s="72">
+      <c r="F18" s="68">
         <v>25.965083798882681</v>
       </c>
       <c r="G18" s="19"/>
@@ -2554,7 +2582,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="21" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -2564,11 +2592,11 @@
       <c r="C2" s="94"/>
       <c r="D2" s="94"/>
       <c r="E2" s="95"/>
-      <c r="F2" s="82"/>
+      <c r="F2" s="78"/>
     </row>
     <row r="3" spans="1:30" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="88" t="s">
-        <v>145</v>
+      <c r="A3" s="84" t="s">
+        <v>144</v>
       </c>
       <c r="B3" s="25">
         <v>2021</v>
@@ -2579,11 +2607,11 @@
       <c r="D3" s="25">
         <v>2023</v>
       </c>
-      <c r="E3" s="81">
+      <c r="E3" s="77">
         <v>2024</v>
       </c>
-      <c r="F3" s="88" t="s">
-        <v>135</v>
+      <c r="F3" s="84" t="s">
+        <v>134</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>84</v>
@@ -2647,7 +2675,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.4">
-      <c r="A4" s="88" t="s">
+      <c r="A4" s="84" t="s">
         <v>89</v>
       </c>
       <c r="B4" s="25">
@@ -2659,10 +2687,10 @@
       <c r="D4" s="25">
         <v>89</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="77">
         <v>89</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="29">
         <f>AVERAGE(B4:E4)</f>
         <v>104.25</v>
       </c>
@@ -2728,22 +2756,22 @@
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.4">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="82">
+      <c r="B5" s="78">
         <v>207</v>
       </c>
-      <c r="C5" s="82">
+      <c r="C5" s="78">
         <v>239</v>
       </c>
-      <c r="D5" s="82">
+      <c r="D5" s="78">
         <v>175</v>
       </c>
-      <c r="E5" s="83">
+      <c r="E5" s="79">
         <v>175</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <f t="shared" ref="F5:F8" si="0">AVERAGE(B5:E5)</f>
         <v>199</v>
       </c>
@@ -2809,22 +2837,22 @@
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.4">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="82">
+      <c r="B6" s="78">
         <v>249</v>
       </c>
-      <c r="C6" s="82">
+      <c r="C6" s="78">
         <v>284</v>
       </c>
-      <c r="D6" s="82">
+      <c r="D6" s="78">
         <v>461</v>
       </c>
-      <c r="E6" s="83">
+      <c r="E6" s="79">
         <v>461</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <f t="shared" si="0"/>
         <v>363.75</v>
       </c>
@@ -2890,22 +2918,22 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="84">
+      <c r="B7" s="80">
         <v>1091</v>
       </c>
-      <c r="C7" s="84">
+      <c r="C7" s="80">
         <v>804</v>
       </c>
-      <c r="D7" s="84">
+      <c r="D7" s="80">
         <v>836</v>
       </c>
-      <c r="E7" s="85">
+      <c r="E7" s="81">
         <v>836</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="31">
         <f t="shared" si="0"/>
         <v>891.75</v>
       </c>
@@ -2971,22 +2999,22 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="87" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" s="84">
+      <c r="A8" s="83" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="80">
         <v>1686</v>
       </c>
-      <c r="C8" s="84">
+      <c r="C8" s="80">
         <v>1427</v>
       </c>
-      <c r="D8" s="84">
+      <c r="D8" s="80">
         <v>1561</v>
       </c>
-      <c r="E8" s="85">
+      <c r="E8" s="81">
         <v>1561</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="31">
         <f t="shared" si="0"/>
         <v>1558.75</v>
       </c>
@@ -3052,12 +3080,12 @@
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.4">
-      <c r="A9" s="82"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
       <c r="H9" t="s">
         <v>89</v>
       </c>
@@ -3120,23 +3148,23 @@
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.4">
-      <c r="A10" s="82" t="s">
-        <v>147</v>
-      </c>
-      <c r="B10" s="82" cm="1">
+      <c r="A10" s="78" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="78" cm="1">
         <f t="array" ref="B10:E10">TRANSPOSE('[1]MLS Yearbook 2020-2024'!I62:I65)</f>
         <v>47</v>
       </c>
-      <c r="C10" s="82">
+      <c r="C10" s="78">
         <v>30</v>
       </c>
-      <c r="D10" s="82">
+      <c r="D10" s="78">
         <v>25</v>
       </c>
-      <c r="E10" s="82">
+      <c r="E10" s="78">
         <v>13</v>
       </c>
-      <c r="F10" s="82"/>
+      <c r="F10" s="78"/>
       <c r="H10" t="s">
         <v>89</v>
       </c>
@@ -3199,26 +3227,26 @@
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.4">
-      <c r="A11" s="82" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11" s="82">
+      <c r="A11" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="78">
         <f>B5+B10</f>
         <v>254</v>
       </c>
-      <c r="C11" s="82">
+      <c r="C11" s="78">
         <f t="shared" ref="C11:E11" si="1">C5+C10</f>
         <v>269</v>
       </c>
-      <c r="D11" s="82">
+      <c r="D11" s="78">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="E11" s="82">
+      <c r="E11" s="78">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
-      <c r="F11" s="82"/>
+      <c r="F11" s="78"/>
       <c r="H11" t="s">
         <v>89</v>
       </c>
